--- a/reports/IPAYOUT - New Relic agent status (TEST).xlsx
+++ b/reports/IPAYOUT - New Relic agent status (TEST).xlsx
@@ -56,13 +56,15 @@
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="46" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="15" customWidth="1"/>
+    <col min="4" max="4" width="48" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
     <col min="7" max="7" width="28" customWidth="1"/>
-    <col min="8" max="8" width="20" customWidth="1"/>
-    <col min="9" max="9" width="60" customWidth="1"/>
-    <col min="10" max="10" width="58" customWidth="1"/>
+    <col min="8" max="8" width="22" customWidth="1"/>
+    <col min="9" max="9" width="18" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="11" max="11" width="16" customWidth="1"/>
+    <col min="12" max="12" width="95" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -88,12 +90,12 @@
       </c>
       <c r="E1" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Agent installed</t>
+          <t xml:space="preserve">Infra agent</t>
         </is>
       </c>
       <c r="F1" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Agent version</t>
+          <t xml:space="preserve">Infra version</t>
         </is>
       </c>
       <c r="G1" t="inlineStr" s="1">
@@ -108,10 +110,20 @@
       </c>
       <c r="I1" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Stopped IPS services</t>
+          <t xml:space="preserve">.NET agent (APM)</t>
         </is>
       </c>
       <c r="J1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">.NET version</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">APM applications</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Notes</t>
         </is>
@@ -160,12 +172,22 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not reporting to New Relic - agent not installed</t>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No agent installed</t>
         </is>
       </c>
     </row>
@@ -212,12 +234,22 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not reporting to New Relic - agent not installed</t>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No agent installed</t>
         </is>
       </c>
     </row>
@@ -264,12 +296,22 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ips_deploymentservice</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IIS is running but no .NET agent: 0 transactions in 30 days</t>
         </is>
       </c>
     </row>
@@ -296,32 +338,42 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">1.80.3</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">292</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not reporting to New Relic - agent not installed</t>
+          <t xml:space="preserve">10.54.0</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reports as the default name 'My Application' - remove &lt;name&gt; from newrelic.config so apps are named by app pool</t>
         </is>
       </c>
     </row>
@@ -368,10 +420,20 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ips_deploymentservice</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10.54.0</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
         </is>
@@ -420,10 +482,20 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">ips_deploymentservice</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10.54.0</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
         </is>
@@ -472,12 +544,22 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not reporting to New Relic - agent not installed</t>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No agent installed. Also needs the nri-mssql integration</t>
         </is>
       </c>
     </row>
@@ -524,12 +606,22 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not reporting to New Relic - agent not installed</t>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No agent installed. Also needs the nri-mssql integration</t>
         </is>
       </c>
     </row>
@@ -576,12 +668,22 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">ips_sendunsentachsservice, ips_svcorderprocessorservice, ips_recurringtransfersservice, ips_emailreceiverservice, ips_deploymentservice, ips_deletefilemanagerservice, ips_bai2reportsservice, ips_achreportservice</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t xml:space="preserve">8 IPS services stopped - needs review</t>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8 IPS services stopped. Needs the .NET agent plus the CORECLR variables, since the services do not run under IIS</t>
         </is>
       </c>
     </row>
@@ -628,12 +730,22 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reports as UE1-TEST-SMT-A1 (name mismatch, likely the same host)</t>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reports as UE1-TEST-SMT-A1 (name mismatch, likely the 15-char NetBIOS limit)</t>
         </is>
       </c>
     </row>
@@ -680,16 +792,26 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not reporting. Windows Services integration does not apply (Linux)</t>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Needs the Linux agent. Windows Services and the .NET agent do not apply</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J12"/>
+  <autoFilter ref="A1:L12"/>
 </worksheet>
 </file>